--- a/artfynd/A 830-2026 artfynd.xlsx
+++ b/artfynd/A 830-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>92071375</v>
+        <v>97090623</v>
       </c>
       <c r="B2" t="n">
-        <v>97533</v>
+        <v>99153</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>219874</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Åmot, Söndagsåsen, Gstr</t>
+          <t>KÄMPOBERGET, HÖGSTA TOPPEN, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580411</v>
+        <v>580456</v>
       </c>
       <c r="R2" t="n">
-        <v>6756794</v>
+        <v>6756565</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -738,11 +738,6 @@
           <t>Ockelbo</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Gst Fyndnr 222197N</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
           <t>2000-07-11</t>
@@ -764,23 +759,23 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>skog, Granskog, ung skog, i körväg, igengräsad</t>
+          <t>SKOG, BLANDSKOG, YNGRE, LUCKIG, PÅ BLOCKRIK MORÄN, I SKOGSBYGD</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>Gst Fyndnr 222189N</t>
+          <t>Gst Fyndnr 215281N</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Peter Ståhl</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Peter Ståhl</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -794,7 +789,7 @@
         <v>92071379</v>
       </c>
       <c r="B3" t="n">
-        <v>97530</v>
+        <v>97983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97090623</v>
+        <v>92071375</v>
       </c>
       <c r="B4" t="n">
-        <v>98693</v>
+        <v>97986</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,34 +913,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219874</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>KÄMPOBERGET, HÖGSTA TOPPEN, Gstr</t>
+          <t>Åmot, Söndagsåsen, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580456</v>
+        <v>580411</v>
       </c>
       <c r="R4" t="n">
-        <v>6756565</v>
+        <v>6756794</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -970,6 +965,11 @@
           <t>Ockelbo</t>
         </is>
       </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Gst Fyndnr 222197N</t>
+        </is>
+      </c>
       <c r="Y4" t="inlineStr">
         <is>
           <t>2000-07-11</t>
@@ -991,23 +991,23 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>SKOG, BLANDSKOG, YNGRE, LUCKIG, PÅ BLOCKRIK MORÄN, I SKOGSBYGD</t>
+          <t>skog, Granskog, ung skog, i körväg, igengräsad</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>Gst Fyndnr 215281N</t>
+          <t>Gst Fyndnr 222189N</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Peter Ståhl</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Peter Ståhl</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
